--- a/Equiv/2024/Person_data_conversion.xlsx
+++ b/Equiv/2024/Person_data_conversion.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E3B708-6C1D-4397-B7C3-3C04A4BDA03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5320CF1-B0DD-429D-85EC-AA4B40B08599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="age" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="176">
   <si>
     <t>Value</t>
   </si>
@@ -637,12 +637,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9410,14 +9408,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9431,7 +9429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -9445,7 +9443,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -9458,44 +9456,8 @@
       <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="3">
-        <v>964121</v>
-      </c>
-      <c r="K3" s="3">
-        <v>968772</v>
-      </c>
-      <c r="L3" s="3">
-        <v>969848</v>
-      </c>
-      <c r="M3" s="3">
-        <v>1025207</v>
-      </c>
-      <c r="N3" s="3">
-        <v>1037627</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0.51</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0.498</v>
-      </c>
-      <c r="S3" s="4">
-        <v>0.48599999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
@@ -9508,44 +9470,8 @@
       <c r="D4" t="s">
         <v>45</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="3">
-        <v>907297</v>
-      </c>
-      <c r="K4" s="3">
-        <v>904946</v>
-      </c>
-      <c r="L4" s="3">
-        <v>858455</v>
-      </c>
-      <c r="M4" s="3">
-        <v>953677</v>
-      </c>
-      <c r="N4" s="3">
-        <v>991025</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0.437</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0.46300000000000002</v>
-      </c>
-      <c r="S4" s="4">
-        <v>0.46400000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -9558,20 +9484,8 @@
       <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5">
-        <v>803</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -9584,32 +9498,8 @@
       <c r="D6" t="s">
         <v>45</v>
       </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1302</v>
-      </c>
-      <c r="L6" s="3">
-        <v>16194</v>
-      </c>
-      <c r="M6" s="3">
-        <v>24062</v>
-      </c>
-      <c r="P6" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="R6" s="4">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -9622,32 +9512,8 @@
       <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="H7">
-        <v>997</v>
-      </c>
-      <c r="I7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" s="3">
-        <v>17791</v>
-      </c>
-      <c r="M7">
-        <v>671</v>
-      </c>
-      <c r="N7">
-        <v>379</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -9657,38 +9523,8 @@
       <c r="C8" t="s">
         <v>149</v>
       </c>
-      <c r="H8">
-        <v>999</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3">
-        <v>24456</v>
-      </c>
-      <c r="L8" s="3">
-        <v>103943</v>
-      </c>
-      <c r="M8" s="3">
-        <v>57001</v>
-      </c>
-      <c r="N8" s="3">
-        <v>106103</v>
-      </c>
-      <c r="P8" s="4">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="R8" s="4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -9701,23 +9537,8 @@
       <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="H9">
-        <v>995</v>
-      </c>
-      <c r="I9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3">
-        <v>23959</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2016</v>
       </c>
@@ -9731,7 +9552,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2016</v>
       </c>
@@ -9745,7 +9566,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2016</v>
       </c>
@@ -9759,7 +9580,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -9773,7 +9594,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2016</v>
       </c>
@@ -9787,7 +9608,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2016</v>
       </c>
@@ -9798,7 +9619,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -14738,14 +14559,14 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -14759,7 +14580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -14772,44 +14593,8 @@
       <c r="D2" t="s">
         <v>163</v>
       </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="3">
-        <v>746661</v>
-      </c>
-      <c r="J2" s="3">
-        <v>760112</v>
-      </c>
-      <c r="K2" s="3">
-        <v>875523</v>
-      </c>
-      <c r="L2" s="3">
-        <v>849230</v>
-      </c>
-      <c r="M2" s="3">
-        <v>899103</v>
-      </c>
-      <c r="N2" s="4">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0.55900000000000005</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0.629</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0.54600000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -14822,44 +14607,8 @@
       <c r="D3" t="s">
         <v>163</v>
       </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" s="3">
-        <v>419219</v>
-      </c>
-      <c r="J3" s="3">
-        <v>402124</v>
-      </c>
-      <c r="K3" s="3">
-        <v>373737</v>
-      </c>
-      <c r="L3" s="3">
-        <v>446132</v>
-      </c>
-      <c r="M3" s="3">
-        <v>469301</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0.312</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0.29599999999999999</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0.27900000000000003</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0.28499999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
@@ -14872,44 +14621,8 @@
       <c r="D4" t="s">
         <v>163</v>
       </c>
-      <c r="G4">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="3">
-        <v>99310</v>
-      </c>
-      <c r="J4" s="3">
-        <v>113693</v>
-      </c>
-      <c r="K4" s="3">
-        <v>95696</v>
-      </c>
-      <c r="L4" s="3">
-        <v>89286</v>
-      </c>
-      <c r="M4" s="3">
-        <v>85225</v>
-      </c>
-      <c r="N4" s="4">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="O4" s="4">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="P4" s="4">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="R4" s="4">
-        <v>5.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -14922,44 +14635,8 @@
       <c r="D5" t="s">
         <v>163</v>
       </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I5" s="3">
-        <v>19779</v>
-      </c>
-      <c r="J5" s="3">
-        <v>31847</v>
-      </c>
-      <c r="K5" s="3">
-        <v>14359</v>
-      </c>
-      <c r="L5" s="3">
-        <v>20325</v>
-      </c>
-      <c r="M5" s="3">
-        <v>18085</v>
-      </c>
-      <c r="N5" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O5" s="4">
-        <v>2.3E-2</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="R5" s="4">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -14972,44 +14649,8 @@
       <c r="D6" t="s">
         <v>163</v>
       </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s">
-        <v>134</v>
-      </c>
-      <c r="I6" s="3">
-        <v>3366</v>
-      </c>
-      <c r="J6" s="3">
-        <v>2797</v>
-      </c>
-      <c r="K6">
-        <v>272</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1594</v>
-      </c>
-      <c r="M6" s="3">
-        <v>6704</v>
-      </c>
-      <c r="N6" s="4">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="O6" s="4">
-        <v>2E-3</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="R6" s="4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -15022,38 +14663,8 @@
       <c r="D7" t="s">
         <v>163</v>
       </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>135</v>
-      </c>
-      <c r="I7">
-        <v>120</v>
-      </c>
-      <c r="J7">
-        <v>207</v>
-      </c>
-      <c r="K7">
-        <v>580</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1143</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -15066,38 +14677,8 @@
       <c r="D8" t="s">
         <v>136</v>
       </c>
-      <c r="G8">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>136</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7746</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1032</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3497</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5438</v>
-      </c>
-      <c r="N8" s="4">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="O8" s="4">
-        <v>1E-3</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>2E-3</v>
-      </c>
-      <c r="R8" s="4">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -15110,44 +14691,8 @@
       <c r="D9" t="s">
         <v>137</v>
       </c>
-      <c r="G9">
-        <v>996</v>
-      </c>
-      <c r="H9" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="3">
-        <v>25404</v>
-      </c>
-      <c r="J9" s="3">
-        <v>20167</v>
-      </c>
-      <c r="K9" s="3">
-        <v>25868</v>
-      </c>
-      <c r="L9" s="3">
-        <v>166219</v>
-      </c>
-      <c r="M9" s="3">
-        <v>119567</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1.9E-2</v>
-      </c>
-      <c r="O9" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P9" s="4">
-        <v>1.9E-2</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>0.104</v>
-      </c>
-      <c r="R9" s="4">
-        <v>7.2999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2021</v>
       </c>
@@ -15160,44 +14705,8 @@
       <c r="D10" t="s">
         <v>138</v>
       </c>
-      <c r="G10">
-        <v>997</v>
-      </c>
-      <c r="H10" t="s">
-        <v>138</v>
-      </c>
-      <c r="I10" s="3">
-        <v>21265</v>
-      </c>
-      <c r="J10" s="3">
-        <v>28573</v>
-      </c>
-      <c r="K10" s="3">
-        <v>6786</v>
-      </c>
-      <c r="L10" s="3">
-        <v>19211</v>
-      </c>
-      <c r="M10" s="3">
-        <v>43197</v>
-      </c>
-      <c r="N10" s="4">
-        <v>1.6E-2</v>
-      </c>
-      <c r="O10" s="4">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="P10" s="4">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>1.2E-2</v>
-      </c>
-      <c r="R10" s="4">
-        <v>2.5999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2021</v>
       </c>
@@ -15207,14 +14716,8 @@
       <c r="C11" t="s">
         <v>149</v>
       </c>
-      <c r="G11">
-        <v>995</v>
-      </c>
-      <c r="H11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2018</v>
       </c>
@@ -15228,7 +14731,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2018</v>
       </c>
@@ -15242,7 +14745,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2018</v>
       </c>
@@ -15256,7 +14759,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2018</v>
       </c>
@@ -15270,7 +14773,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2018</v>
       </c>
@@ -16623,13 +16126,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16643,7 +16146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -16657,7 +16160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
@@ -16670,44 +16173,8 @@
       <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="3">
-        <v>65834</v>
-      </c>
-      <c r="L3" s="3">
-        <v>48656</v>
-      </c>
-      <c r="M3" s="3">
-        <v>37056</v>
-      </c>
-      <c r="N3" s="3">
-        <v>34989</v>
-      </c>
-      <c r="O3" s="3">
-        <v>29164</v>
-      </c>
-      <c r="P3" s="4">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="R3" s="4">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="S3" s="4">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="T3" s="4">
-        <v>1.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
@@ -16720,44 +16187,8 @@
       <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="3">
-        <v>266417</v>
-      </c>
-      <c r="L4" s="3">
-        <v>263839</v>
-      </c>
-      <c r="M4" s="3">
-        <v>135248</v>
-      </c>
-      <c r="N4" s="3">
-        <v>206697</v>
-      </c>
-      <c r="O4" s="3">
-        <v>144131</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0.187</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0.09</v>
-      </c>
-      <c r="S4" s="4">
-        <v>0.129</v>
-      </c>
-      <c r="T4" s="4">
-        <v>8.7999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
@@ -16770,44 +16201,8 @@
       <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="3">
-        <v>175161</v>
-      </c>
-      <c r="L5" s="3">
-        <v>188056</v>
-      </c>
-      <c r="M5" s="3">
-        <v>165007</v>
-      </c>
-      <c r="N5" s="3">
-        <v>153907</v>
-      </c>
-      <c r="O5" s="3">
-        <v>168429</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0.123</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0.129</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0.109</v>
-      </c>
-      <c r="S5" s="4">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0.10199999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -16820,44 +16215,8 @@
       <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="3">
-        <v>78696</v>
-      </c>
-      <c r="L6" s="3">
-        <v>74649</v>
-      </c>
-      <c r="M6" s="3">
-        <v>59387</v>
-      </c>
-      <c r="N6" s="3">
-        <v>77916</v>
-      </c>
-      <c r="O6" s="3">
-        <v>64427</v>
-      </c>
-      <c r="P6" s="4">
-        <v>5.5E-2</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="R6" s="4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="S6" s="4">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="T6" s="4">
-        <v>3.9E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -16870,44 +16229,8 @@
       <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="3">
-        <v>85468</v>
-      </c>
-      <c r="L7" s="3">
-        <v>103232</v>
-      </c>
-      <c r="M7" s="3">
-        <v>86646</v>
-      </c>
-      <c r="N7" s="3">
-        <v>103144</v>
-      </c>
-      <c r="O7" s="3">
-        <v>91449</v>
-      </c>
-      <c r="P7" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="R7" s="4">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="S7" s="4">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="T7" s="4">
-        <v>5.6000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -16920,44 +16243,8 @@
       <c r="D8" t="s">
         <v>37</v>
       </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" s="3">
-        <v>417295</v>
-      </c>
-      <c r="L8" s="3">
-        <v>445334</v>
-      </c>
-      <c r="M8" s="3">
-        <v>537989</v>
-      </c>
-      <c r="N8" s="3">
-        <v>504513</v>
-      </c>
-      <c r="O8" s="3">
-        <v>551645</v>
-      </c>
-      <c r="P8" s="4">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="R8" s="4">
-        <v>0.35599999999999998</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0.316</v>
-      </c>
-      <c r="T8" s="4">
-        <v>0.33500000000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -16970,44 +16257,8 @@
       <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="3">
-        <v>337517</v>
-      </c>
-      <c r="L9" s="3">
-        <v>334644</v>
-      </c>
-      <c r="M9" s="3">
-        <v>410221</v>
-      </c>
-      <c r="N9" s="3">
-        <v>472259</v>
-      </c>
-      <c r="O9" s="3">
-        <v>507954</v>
-      </c>
-      <c r="P9" s="4">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="R9" s="4">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="S9" s="4">
-        <v>0.29599999999999999</v>
-      </c>
-      <c r="T9" s="4">
-        <v>0.309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2021</v>
       </c>
@@ -17017,32 +16268,8 @@
       <c r="C10" t="s">
         <v>149</v>
       </c>
-      <c r="I10">
-        <v>999</v>
-      </c>
-      <c r="J10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="3">
-        <v>78416</v>
-      </c>
-      <c r="N10" s="3">
-        <v>42736</v>
-      </c>
-      <c r="O10" s="3">
-        <v>87052</v>
-      </c>
-      <c r="R10" s="4">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="S10" s="4">
-        <v>2.7E-2</v>
-      </c>
-      <c r="T10" s="4">
-        <v>5.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2016</v>
       </c>
@@ -17055,29 +16282,8 @@
       <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="I11">
-        <v>995</v>
-      </c>
-      <c r="J11" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="3">
-        <v>445030</v>
-      </c>
-      <c r="L11" s="3">
-        <v>441871</v>
-      </c>
-      <c r="M11" s="3">
-        <v>456262</v>
-      </c>
-      <c r="N11" s="3">
-        <v>464456</v>
-      </c>
-      <c r="O11" s="3">
-        <v>514841</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2016</v>
       </c>
@@ -17091,7 +16297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2016</v>
       </c>
@@ -17105,7 +16311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2016</v>
       </c>
@@ -17119,7 +16325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2016</v>
       </c>
@@ -17133,7 +16339,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2016</v>
       </c>
@@ -17562,13 +16768,13 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="49.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -17582,7 +16788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2016</v>
       </c>
@@ -17595,44 +16801,8 @@
       <c r="D2" t="s">
         <v>107</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="3">
-        <v>19906</v>
-      </c>
-      <c r="I2" s="3">
-        <v>17704</v>
-      </c>
-      <c r="J2" s="3">
-        <v>9484</v>
-      </c>
-      <c r="K2" s="3">
-        <v>44553</v>
-      </c>
-      <c r="L2" s="3">
-        <v>28438</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="N2" s="4">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="O2" s="4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="P2" s="4">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>5.6000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2016</v>
       </c>
@@ -17645,44 +16815,8 @@
       <c r="D3" t="s">
         <v>106</v>
       </c>
-      <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="3">
-        <v>110008</v>
-      </c>
-      <c r="I3" s="3">
-        <v>123535</v>
-      </c>
-      <c r="J3" s="3">
-        <v>11600</v>
-      </c>
-      <c r="K3" s="3">
-        <v>128399</v>
-      </c>
-      <c r="L3" s="3">
-        <v>109450</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0.22</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0.255</v>
-      </c>
-      <c r="O3" s="4">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0.255</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0.214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2016</v>
       </c>
@@ -17695,44 +16829,8 @@
       <c r="D4" t="s">
         <v>109</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="3">
-        <v>328330</v>
-      </c>
-      <c r="I4" s="3">
-        <v>276660</v>
-      </c>
-      <c r="J4" s="3">
-        <v>192426</v>
-      </c>
-      <c r="K4" s="3">
-        <v>238931</v>
-      </c>
-      <c r="L4" s="3">
-        <v>293264</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0.57099999999999995</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0.79200000000000004</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0.57399999999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -17745,32 +16843,8 @@
       <c r="D5" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F5">
-        <v>101</v>
-      </c>
-      <c r="G5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J5" s="3">
-        <v>6477</v>
-      </c>
-      <c r="K5" s="3">
-        <v>5754</v>
-      </c>
-      <c r="L5" s="3">
-        <v>12553</v>
-      </c>
-      <c r="O5" s="4">
-        <v>2.7E-2</v>
-      </c>
-      <c r="P5" s="4">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>2.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2016</v>
       </c>
@@ -17783,44 +16857,8 @@
       <c r="D6" t="s">
         <v>111</v>
       </c>
-      <c r="F6">
-        <v>102</v>
-      </c>
-      <c r="G6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="3">
-        <v>23053</v>
-      </c>
-      <c r="I6" s="3">
-        <v>35240</v>
-      </c>
-      <c r="J6" s="3">
-        <v>4562</v>
-      </c>
-      <c r="K6" s="3">
-        <v>41658</v>
-      </c>
-      <c r="L6" s="3">
-        <v>44521</v>
-      </c>
-      <c r="M6" s="4">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="N6" s="4">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="O6" s="4">
-        <v>1.9E-2</v>
-      </c>
-      <c r="P6" s="4">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>8.6999999999999994E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2016</v>
       </c>
@@ -17833,44 +16871,8 @@
       <c r="D7" t="s">
         <v>112</v>
       </c>
-      <c r="F7">
-        <v>103</v>
-      </c>
-      <c r="G7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H7" s="3">
-        <v>10171</v>
-      </c>
-      <c r="I7" s="3">
-        <v>12936</v>
-      </c>
-      <c r="J7" s="3">
-        <v>7924</v>
-      </c>
-      <c r="K7" s="3">
-        <v>27306</v>
-      </c>
-      <c r="L7" s="3">
-        <v>6353</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="N7" s="4">
-        <v>2.7E-2</v>
-      </c>
-      <c r="O7" s="4">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="P7" s="4">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2016</v>
       </c>
@@ -17883,20 +16885,8 @@
       <c r="D8" t="s">
         <v>108</v>
       </c>
-      <c r="F8">
-        <v>104</v>
-      </c>
-      <c r="G8" t="s">
-        <v>108</v>
-      </c>
-      <c r="K8">
-        <v>193</v>
-      </c>
-      <c r="P8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2016</v>
       </c>
@@ -17909,26 +16899,8 @@
       <c r="D9" t="s">
         <v>113</v>
       </c>
-      <c r="F9">
-        <v>106</v>
-      </c>
-      <c r="G9" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3564</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2048</v>
-      </c>
-      <c r="N9" s="4">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Q9" s="4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2016</v>
       </c>
@@ -17941,32 +16913,8 @@
       <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="F10">
-        <v>107</v>
-      </c>
-      <c r="G10" t="s">
-        <v>114</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1975</v>
-      </c>
-      <c r="I10">
-        <v>48</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1312</v>
-      </c>
-      <c r="M10" s="4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2016</v>
       </c>
@@ -17979,44 +16927,8 @@
       <c r="D11" t="s">
         <v>45</v>
       </c>
-      <c r="F11">
-        <v>997</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="3">
-        <v>6490</v>
-      </c>
-      <c r="I11" s="3">
-        <v>14699</v>
-      </c>
-      <c r="J11" s="3">
-        <v>10498</v>
-      </c>
-      <c r="K11" s="3">
-        <v>15343</v>
-      </c>
-      <c r="L11" s="3">
-        <v>14043</v>
-      </c>
-      <c r="M11" s="4">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="O11" s="4">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="P11" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2016</v>
       </c>
@@ -18026,14 +16938,8 @@
       <c r="C12" t="s">
         <v>149</v>
       </c>
-      <c r="F12">
-        <v>995</v>
-      </c>
-      <c r="G12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2021</v>
       </c>
@@ -18047,7 +16953,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2021</v>
       </c>
@@ -18061,7 +16967,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2021</v>
       </c>
@@ -18075,7 +16981,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2021</v>
       </c>
